--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_los_rios.xlsx
@@ -375,76 +375,76 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>14101</t>
+          <t>14203</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Valdivia</t>
+          <t>Lago Ranco</t>
         </is>
       </c>
       <c r="C2">
-        <v>134868</v>
+        <v>93.43960195337695</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>14201</t>
+          <t>14106</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>La Unión</t>
+          <t>Mariquina</t>
         </is>
       </c>
       <c r="C3">
-        <v>35238</v>
+        <v>93.15014975908322</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>14108</t>
+          <t>14202</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Panguipulli</t>
+          <t>Futrono</t>
         </is>
       </c>
       <c r="C4">
-        <v>34896</v>
+        <v>92.56881866436242</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>14106</t>
+          <t>14102</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Mariquina</t>
+          <t>Corral</t>
         </is>
       </c>
       <c r="C5">
-        <v>21459</v>
+        <v>92.51389992057189</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>14104</t>
+          <t>14103</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Lanco</t>
         </is>
       </c>
       <c r="C6">
-        <v>19518</v>
+        <v>92.44711326575585</v>
       </c>
     </row>
     <row r="7">
@@ -459,82 +459,82 @@
         </is>
       </c>
       <c r="C7">
-        <v>19412</v>
+        <v>92.44689970473378</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>14103</t>
+          <t>14105</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Lanco</t>
+          <t>Máfil</t>
         </is>
       </c>
       <c r="C8">
-        <v>16781</v>
+        <v>92.34480959833073</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>14202</t>
+          <t>14104</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Futrono</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="C9">
-        <v>14998</v>
+        <v>92.24007561436673</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>14203</t>
+          <t>14108</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lago Ranco</t>
+          <t>Panguipulli</t>
         </is>
       </c>
       <c r="C10">
-        <v>10141</v>
+        <v>92.10060967563145</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>14105</t>
+          <t>14201</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Máfil</t>
+          <t>La Unión</t>
         </is>
       </c>
       <c r="C11">
-        <v>7081</v>
+        <v>87.69161855464861</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>14102</t>
+          <t>14101</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Corral</t>
+          <t>Valdivia</t>
         </is>
       </c>
       <c r="C12">
-        <v>4659</v>
+        <v>80.09597168360226</v>
       </c>
     </row>
   </sheetData>
@@ -590,7 +590,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">

--- a/output/laminas_comunales/comunal_s_fonasa_a_2021_los_rios.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2021_los_rios.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C375"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -535,6 +535,5451 @@
       </c>
       <c r="C12">
         <v>80.09597168360226</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C13">
+        <v>48.0474330888656</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C14">
+        <v>47.77805209233428</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C15">
+        <v>47.60907888937858</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C16">
+        <v>47.55758538522637</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C17">
+        <v>47.49838754261494</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C18">
+        <v>47.24830464267084</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C19">
+        <v>47.10338092850168</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C20">
+        <v>46.98960302457467</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>46.90280852541564</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C22">
+        <v>46.24734123366758</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C23">
+        <v>45.941214410762</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C24">
+        <v>45.40364324109098</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C25">
+        <v>45.25047258979206</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C26">
+        <v>45.09650495565989</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C27">
+        <v>44.99722874712977</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C28">
+        <v>44.95631453534551</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C29">
+        <v>44.83803437637726</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C30">
+        <v>44.79076657202815</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C31">
+        <v>44.39946661586818</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C32">
+        <v>42.57674468325187</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C33">
+        <v>42.28797531355764</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C34">
+        <v>38.8751309648538</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C35">
+        <v>38.28638263985666</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C36">
+        <v>37.51922700035039</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C37">
+        <v>37.32608495346908</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C38">
+        <v>37.05576559546314</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C39">
+        <v>36.81644241451673</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C40">
+        <v>36.77831643895989</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C41">
+        <v>35.64162754303599</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C42">
+        <v>35.46034639927074</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C43">
+        <v>34.69608593523186</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C44">
+        <v>34.23351866560763</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C45">
+        <v>33.44518152069983</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C46">
+        <v>30.4257172266357</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C47">
+        <v>30.36026905003225</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C48">
+        <v>27.77998411437649</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C49">
+        <v>26.04071710726223</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C50">
+        <v>25.96593013208246</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C51">
+        <v>24.5923314235346</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C52">
+        <v>24.32185706833594</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C53">
+        <v>23.630821983046</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C54">
+        <v>22.45746691871456</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C55">
+        <v>20.57868074568098</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C56">
+        <v>20.52686489306208</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C57">
+        <v>19.86803837305205</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C58">
+        <v>19.78733459357278</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C59">
+        <v>19.51771849492335</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C60">
+        <v>19.00317712470214</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C61">
+        <v>18.55993829881005</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C62">
+        <v>18.47896861570517</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C63">
+        <v>18.03951821620545</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C64">
+        <v>17.87433650166646</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C65">
+        <v>17.32069720925803</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C66">
+        <v>17.13661636219222</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C67">
+        <v>16.9546969509937</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C68">
+        <v>16.67584839136183</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C69">
+        <v>16.65127081738763</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C70">
+        <v>16.64461247637051</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C71">
+        <v>16.27297837889323</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C72">
+        <v>16.25357044135262</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C73">
+        <v>16.10589462702139</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C74">
+        <v>15.82972450013821</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C75">
+        <v>15.68705321683876</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C76">
+        <v>15.28240784836651</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C77">
+        <v>15.03833522386464</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C78">
+        <v>14.98435054773083</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C79">
+        <v>14.91725830716039</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C80">
+        <v>14.87990304098722</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C81">
+        <v>14.74218594465459</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C82">
+        <v>14.7148253939003</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C83">
+        <v>14.47542533081285</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C84">
+        <v>14.23203264981087</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C85">
+        <v>14.18153405391327</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C86">
+        <v>13.99903790762725</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C87">
+        <v>13.97239304283565</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C88">
+        <v>13.79117844437978</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C89">
+        <v>13.6649737378999</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C90">
+        <v>13.57589984350548</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C91">
+        <v>13.53536600419701</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C92">
+        <v>13.4489569188989</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C93">
+        <v>13.43102688408991</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C94">
+        <v>13.20824589556845</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C95">
+        <v>13.12982188779884</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C96">
+        <v>13.07895993401919</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C97">
+        <v>13.02752777851091</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C98">
+        <v>13.01984877126654</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C99">
+        <v>13.00567107750473</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C100">
+        <v>12.96946343265856</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C101">
+        <v>12.9627589246364</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C102">
+        <v>12.93950850661626</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C103">
+        <v>12.90706910246227</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C104">
+        <v>12.83174916676954</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C105">
+        <v>12.81673270063577</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C106">
+        <v>12.80778395552025</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C107">
+        <v>12.76734480959833</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C108">
+        <v>12.73822179198613</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C109">
+        <v>12.6324518566295</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C110">
+        <v>12.62024954757596</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C111">
+        <v>12.56795356122731</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C112">
+        <v>12.52978554408261</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C113">
+        <v>12.5165271044513</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C114">
+        <v>12.47760302608003</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C115">
+        <v>12.4442450315395</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C116">
+        <v>12.40118106486332</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C117">
+        <v>12.33798296506604</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C118">
+        <v>12.31833565598248</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C119">
+        <v>12.31135822081017</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C120">
+        <v>12.2823182530176</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C121">
+        <v>12.23342023838511</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C122">
+        <v>12.21544909038956</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C123">
+        <v>12.18049034950443</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C124">
+        <v>12.0730715095942</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C125">
+        <v>12.07257834079436</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C126">
+        <v>12.06521739130435</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C127">
+        <v>12.0615482066035</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C128">
+        <v>11.98984670515628</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C129">
+        <v>11.85446009389671</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C130">
+        <v>11.84799920366315</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C131">
+        <v>11.7810478794982</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C132">
+        <v>11.77221172022684</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C133">
+        <v>11.73163715062419</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C134">
+        <v>11.72322609078889</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C135">
+        <v>11.64059056853239</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C136">
+        <v>11.58172406928131</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C137">
+        <v>11.5423015149542</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C138">
+        <v>11.49722001588562</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C139">
+        <v>11.41105894627021</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C140">
+        <v>11.38169032426097</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C141">
+        <v>11.33193432909517</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C142">
+        <v>11.31977047470005</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C143">
+        <v>11.30407242207501</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C144">
+        <v>11.25708884688091</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C145">
+        <v>11.13375936535919</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C146">
+        <v>11.07248309362796</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C147">
+        <v>11.05685064037593</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C148">
+        <v>11.03842255597531</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C149">
+        <v>10.83199604987039</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C150">
+        <v>10.82172157833051</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C151">
+        <v>10.61152254087408</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C152">
+        <v>10.43157563411983</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C153">
+        <v>10.34989050368306</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C154">
+        <v>10.32289482905044</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C155">
+        <v>9.967158204806898</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C156">
+        <v>9.134233518665608</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C157">
+        <v>8.326697192912603</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C158">
+        <v>8.196789462119098</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C159">
+        <v>6.841545761745544</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C160">
+        <v>4.807883734819828</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C161">
+        <v>4.668753260302556</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C162">
+        <v>4.201747208952466</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C163">
+        <v>4.11858679320359</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C164">
+        <v>3.988541207580432</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C165">
+        <v>3.963189651430308</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C166">
+        <v>3.847985522430708</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C167">
+        <v>3.709829867674858</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C168">
+        <v>3.653693407466243</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C169">
+        <v>3.566095958590484</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C170">
+        <v>3.518813458092773</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C171">
+        <v>3.345266016541168</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C172">
+        <v>3.234220135628586</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C173">
+        <v>3.229542174685093</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C174">
+        <v>3.108389801820849</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C175">
+        <v>3.068599561713475</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C176">
+        <v>2.883995208698056</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C177">
+        <v>2.784129039154784</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C178">
+        <v>2.637439646520136</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C179">
+        <v>2.52864698104892</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C180">
+        <v>2.509007249207796</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C181">
+        <v>2.496766871651403</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C182">
+        <v>2.476370510396976</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C183">
+        <v>2.454523318862356</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C184">
+        <v>2.409753309839032</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C185">
+        <v>2.343129467831612</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C186">
+        <v>2.285266327360838</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C187">
+        <v>1.863967411430688</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C188">
+        <v>1.861236524463282</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C189">
+        <v>1.839853191830529</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C190">
+        <v>1.704980337301064</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C191">
+        <v>1.687847498014297</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C192">
+        <v>1.682316118935837</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C193">
+        <v>1.612582122237707</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C194">
+        <v>1.597620096959013</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C195">
+        <v>1.505574357953414</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C196">
+        <v>1.484116567586989</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C197">
+        <v>1.48129860511048</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C198">
+        <v>1.463924505442949</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C199">
+        <v>1.459894226531512</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C200">
+        <v>1.454182402222512</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C201">
+        <v>1.438232212591675</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C202">
+        <v>1.43453312467397</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C203">
+        <v>1.391100935695799</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C204">
+        <v>1.37604722837175</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C205">
+        <v>1.353772645829186</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C206">
+        <v>1.310563939634631</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C207">
+        <v>1.239299223571571</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C208">
+        <v>1.233459357277883</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C209">
+        <v>1.22824342673744</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C210">
+        <v>1.167131196496118</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C211">
+        <v>1.162154091180569</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C212">
+        <v>1.160667709963485</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C213">
+        <v>1.102249039392338</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C214">
+        <v>1.066768263644157</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C215">
+        <v>1.022758684234774</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C216">
+        <v>1.017214397496088</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B217" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C217">
+        <v>1.011342155009452</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B218" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C218">
+        <v>1.010352379056341</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B219" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C219">
+        <v>0.9806081974438079</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B220" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C220">
+        <v>0.9506446151842688</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B221" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C221">
+        <v>0.9389671361502347</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B222" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C222">
+        <v>0.928659872368797</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B223" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C223">
+        <v>0.9184723798463934</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B224" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C224">
+        <v>0.9168241965973535</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C225">
+        <v>0.9157873780609198</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C226">
+        <v>0.9052759376072211</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C227">
+        <v>0.8905610058100771</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C228">
+        <v>0.8725094413335069</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C229">
+        <v>0.866119966829448</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C230">
+        <v>0.8498508802026974</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C231">
+        <v>0.8455746204172324</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C232">
+        <v>0.8419330148591939</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C233">
+        <v>0.8412098298676749</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C234">
+        <v>0.837782697399835</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C235">
+        <v>0.8339952343129468</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C236">
+        <v>0.823710929723273</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C237">
+        <v>0.8208187072765183</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C238">
+        <v>0.7988100484795064</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B239" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C239">
+        <v>0.7939508506616257</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B240" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C240">
+        <v>0.7905514810934374</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B241" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C241">
+        <v>0.779773156899811</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C242">
+        <v>0.761497113278917</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B243" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C243">
+        <v>0.7463374182253755</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B244" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C244">
+        <v>0.7390007653936499</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B245" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C245">
+        <v>0.7344772250339464</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C246">
+        <v>0.7148530579825259</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C247">
+        <v>0.7000666730164777</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C248">
+        <v>0.6949960285941224</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C249">
+        <v>0.6911841418883672</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C250">
+        <v>0.6466256697194437</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C251">
+        <v>0.6424447627729305</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C252">
+        <v>0.6390480387836052</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C253">
+        <v>0.6259780907668232</v>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C254">
+        <v>0.6225209343323049</v>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C255">
+        <v>0.6191065815791981</v>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C256">
+        <v>0.6077180188392586</v>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C257">
+        <v>0.6043970545540922</v>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C258">
+        <v>0.5998956703182056</v>
+      </c>
+    </row>
+    <row r="259">
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B259" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C259">
+        <v>0.5957108816521048</v>
+      </c>
+    </row>
+    <row r="260">
+      <c r="A260" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B260" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C260">
+        <v>0.5868544600938967</v>
+      </c>
+    </row>
+    <row r="261">
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B261" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C261">
+        <v>0.5868544600938967</v>
+      </c>
+    </row>
+    <row r="262">
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B262" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C262">
+        <v>0.5863473645228984</v>
+      </c>
+    </row>
+    <row r="263">
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B263" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C263">
+        <v>0.5729396209784046</v>
+      </c>
+    </row>
+    <row r="264">
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B264" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C264">
+        <v>0.5712706164194232</v>
+      </c>
+    </row>
+    <row r="265">
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B265" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C265">
+        <v>0.5556279029387508</v>
+      </c>
+    </row>
+    <row r="266">
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B266" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C266">
+        <v>0.552930056710775</v>
+      </c>
+    </row>
+    <row r="267">
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B267" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C267">
+        <v>0.5477308294209703</v>
+      </c>
+    </row>
+    <row r="268">
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B268" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C268">
+        <v>0.5436284898184833</v>
+      </c>
+    </row>
+    <row r="269">
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B269" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C269">
+        <v>0.5434782608695652</v>
+      </c>
+    </row>
+    <row r="270">
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B270" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C270">
+        <v>0.5361397934868943</v>
+      </c>
+    </row>
+    <row r="271">
+      <c r="A271" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B271" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C271">
+        <v>0.5307986668312554</v>
+      </c>
+    </row>
+    <row r="272">
+      <c r="A272" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B272" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C272">
+        <v>0.5162827640984908</v>
+      </c>
+    </row>
+    <row r="273">
+      <c r="A273" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B273" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C273">
+        <v>0.5159863632175435</v>
+      </c>
+    </row>
+    <row r="274">
+      <c r="A274" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B274" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C274">
+        <v>0.5146612473277205</v>
+      </c>
+    </row>
+    <row r="275">
+      <c r="A275" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B275" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C275">
+        <v>0.5143346985427184</v>
+      </c>
+    </row>
+    <row r="276">
+      <c r="A276" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B276" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C276">
+        <v>0.5123402379903041</v>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B277" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C277">
+        <v>0.5122824342673744</v>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B278" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C278">
+        <v>0.5093826704320515</v>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B279" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C279">
+        <v>0.5078786300299518</v>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B280" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C280">
+        <v>0.5067723210172302</v>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B281" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C281">
+        <v>0.4952852652633584</v>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B282" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C282">
+        <v>0.4903040987219039</v>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C283">
+        <v>0.4875941241821997</v>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C284">
+        <v>0.4847950639048039</v>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C285">
+        <v>0.4791301944162904</v>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C286">
+        <v>0.4737769942706038</v>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C287">
+        <v>0.4631379962192816</v>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C288">
+        <v>0.4618754783710312</v>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C289">
+        <v>0.4601293571211529</v>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C290">
+        <v>0.4434011476264997</v>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C291">
+        <v>0.438425142162608</v>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C292">
+        <v>0.4368546465448769</v>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C293">
+        <v>0.4352137505509035</v>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C294">
+        <v>0.4206049149338374</v>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C295">
+        <v>0.4169976171564734</v>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C296">
+        <v>0.4000380988665587</v>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C297">
+        <v>0.398532555623004</v>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C298">
+        <v>0.3971405877680699</v>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C299">
+        <v>0.3912363067292645</v>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C300">
+        <v>0.3888408838415011</v>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C301">
+        <v>0.3762263072673588</v>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C302">
+        <v>0.3733459357277883</v>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C303">
+        <v>0.3685616880125311</v>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C304">
+        <v>0.3619392323078389</v>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C305">
+        <v>0.3544423440453686</v>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C306">
+        <v>0.351808418713739</v>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C307">
+        <v>0.3409195614115912</v>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C308">
+        <v>0.3342449103615922</v>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C309">
+        <v>0.3332921861498581</v>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C310">
+        <v>0.314315649109439</v>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C311">
+        <v>0.3005053954377817</v>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C312">
+        <v>0.2839155659795087</v>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C313">
+        <v>0.2653993334156277</v>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C314">
+        <v>0.2581413820492454</v>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C315">
+        <v>0.2551984877126654</v>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C316">
+        <v>0.2517688935191214</v>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C317">
+        <v>0.2395650972081452</v>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C318">
+        <v>0.2303510550078319</v>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C319">
+        <v>0.2119229706072054</v>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C320">
+        <v>0.1985702938840349</v>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C321">
+        <v>0.188855169464851</v>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C322">
+        <v>0.1873071837814015</v>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C323">
+        <v>0.1238213163158396</v>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C324">
+        <v>0.1161286917047164</v>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C325">
+        <v>0.1142965996761596</v>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C326">
+        <v>0.1020306589687438</v>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C327">
+        <v>0.09916262670780079</v>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C328">
+        <v>0.09875324034069868</v>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C329">
+        <v>0.07712648743940062</v>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C330">
+        <v>0.07390007653936499</v>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C331">
+        <v>0.07371233760250621</v>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C332">
+        <v>0.0661625708884688</v>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C333">
+        <v>0.05528425320187966</v>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C334">
+        <v>0.05209011590050788</v>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C335">
+        <v>0.04725897920604915</v>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C336">
+        <v>0.03981684252438782</v>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C337">
+        <v>0.03912363067292645</v>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C338">
+        <v>0.037032465127762</v>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C339">
+        <v>0.03038590094196293</v>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C340">
+        <v>0.02608242044861763</v>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C341">
+        <v>0.0198570293884035</v>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C342">
+        <v>0.01842808440062655</v>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C343">
+        <v>0.01068991525272741</v>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C344">
+        <v>0.00868168598341798</v>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C345">
+        <v>0.006172077521293668</v>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C346">
+        <v>0.005509034817100044</v>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C347">
+        <v>0.002639288447834464</v>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C348">
+        <v>0.002488552657774239</v>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C349">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>14101</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>Valdivia</t>
+        </is>
+      </c>
+      <c r="C350">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C351">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C352">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C353">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>14102</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>Corral</t>
+        </is>
+      </c>
+      <c r="C354">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C355">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>14103</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>Lanco</t>
+        </is>
+      </c>
+      <c r="C356">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C357">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C358">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>14104</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
+      <c r="C359">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C360">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C361">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>14105</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Máfil</t>
+        </is>
+      </c>
+      <c r="C362">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C363">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>14106</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Mariquina</t>
+        </is>
+      </c>
+      <c r="C364">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C365">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C366">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>14107</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>Paillaco</t>
+        </is>
+      </c>
+      <c r="C367">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C368">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>14108</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>Panguipulli</t>
+        </is>
+      </c>
+      <c r="C369">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C370">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>14201</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>La Unión</t>
+        </is>
+      </c>
+      <c r="C371">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C372">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>14202</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>Futrono</t>
+        </is>
+      </c>
+      <c r="C373">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C374">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>14203</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>Lago Ranco</t>
+        </is>
+      </c>
+      <c r="C375">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
